--- a/research/traditional_assets/database/data/jordan/jordan_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ16"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.009375</v>
+        <v>0.0101</v>
       </c>
       <c r="E2">
-        <v>-0.0732</v>
+        <v>0.0319</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>754.9399999999999</v>
+        <v>487.68</v>
       </c>
       <c r="L2">
-        <v>0.2227487312640151</v>
+        <v>0.3031893068075847</v>
       </c>
       <c r="M2">
-        <v>388.724</v>
+        <v>243.633</v>
       </c>
       <c r="N2">
-        <v>0.03685670671002854</v>
+        <v>0.05235928735681588</v>
       </c>
       <c r="O2">
-        <v>0.5149071449386706</v>
+        <v>0.4995755413385826</v>
       </c>
       <c r="P2">
-        <v>382.544</v>
+        <v>243.633</v>
       </c>
       <c r="Q2">
-        <v>0.03627075254340138</v>
+        <v>0.05235928735681588</v>
       </c>
       <c r="R2">
-        <v>0.50672106392561</v>
+        <v>0.4995755413385826</v>
       </c>
       <c r="S2">
-        <v>6.18</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.01589816939525216</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>22113.9</v>
+        <v>4888.1</v>
       </c>
       <c r="V2">
-        <v>2.09672036332951</v>
+        <v>1.050503965098536</v>
       </c>
       <c r="W2">
-        <v>0.06916812016889221</v>
+        <v>0.0813183428307408</v>
       </c>
       <c r="X2">
-        <v>0.09845387181587437</v>
+        <v>0.1521713404861267</v>
       </c>
       <c r="Y2">
-        <v>-0.02928575164698216</v>
+        <v>-0.07085299765538591</v>
       </c>
       <c r="Z2">
-        <v>5.55151515151515</v>
+        <v>0.4554463855933403</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07675702716567617</v>
+        <v>0.1174154946527229</v>
       </c>
       <c r="AC2">
-        <v>-0.07675702716567617</v>
+        <v>-0.1174154946527229</v>
       </c>
       <c r="AD2">
-        <v>4422.2</v>
+        <v>3586.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4422.2</v>
+        <v>3586.2</v>
       </c>
       <c r="AG2">
-        <v>-17691.7</v>
+        <v>-1301.900000000001</v>
       </c>
       <c r="AH2">
-        <v>0.2954219024523853</v>
+        <v>0.4352554221839234</v>
       </c>
       <c r="AI2">
-        <v>0.2008329056782005</v>
+        <v>0.3864023273354164</v>
       </c>
       <c r="AJ2">
-        <v>2.476164483260553</v>
+        <v>-0.3884877058963955</v>
       </c>
       <c r="AK2">
-        <v>187.0158562367822</v>
+        <v>-0.2963645883129597</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jordan Islamic Bank (ASE:JOIB)</t>
+          <t>Bank of Jordan (ASE:BOJX)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0381</v>
+        <v>0.0182</v>
       </c>
       <c r="E3">
-        <v>0.0127</v>
+        <v>-0.058</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>83.3</v>
+        <v>52.8</v>
       </c>
       <c r="L3">
-        <v>0.3309495431068732</v>
+        <v>0.2771653543307087</v>
       </c>
       <c r="M3">
-        <v>33.9</v>
+        <v>50.8</v>
       </c>
       <c r="N3">
-        <v>0.03452490070271922</v>
+        <v>0.08348397699260476</v>
       </c>
       <c r="O3">
-        <v>0.4069627851140456</v>
+        <v>0.9621212121212122</v>
       </c>
       <c r="P3">
-        <v>33.9</v>
+        <v>50.8</v>
       </c>
       <c r="Q3">
-        <v>0.03452490070271922</v>
+        <v>0.08348397699260476</v>
       </c>
       <c r="R3">
-        <v>0.4069627851140456</v>
+        <v>0.9621212121212122</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1132.4</v>
+        <v>816.3</v>
       </c>
       <c r="V3">
-        <v>1.153274264181689</v>
+        <v>1.341495480690222</v>
       </c>
       <c r="W3">
-        <v>0.1276237168683928</v>
+        <v>0.0813183428307408</v>
       </c>
       <c r="X3">
-        <v>0.06587557712116589</v>
+        <v>0.1063962723671002</v>
       </c>
       <c r="Y3">
-        <v>0.06174813974722694</v>
+        <v>-0.02507792953635939</v>
       </c>
       <c r="Z3">
-        <v>-0.568813559322034</v>
+        <v>0.8561797752808988</v>
       </c>
       <c r="AA3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06591660835408907</v>
+        <v>0.103332358334463</v>
       </c>
       <c r="AC3">
-        <v>-0.06591660835408907</v>
+        <v>-0.103332358334463</v>
       </c>
       <c r="AD3">
-        <v>20.3</v>
+        <v>87</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>20.3</v>
+        <v>87</v>
       </c>
       <c r="AG3">
-        <v>-1112.1</v>
+        <v>-729.3</v>
       </c>
       <c r="AH3">
-        <v>0.0202554380363201</v>
+        <v>0.1250898634076204</v>
       </c>
       <c r="AI3">
-        <v>0.02805805114029026</v>
+        <v>0.1140235910878113</v>
       </c>
       <c r="AJ3">
-        <v>8.54147465437787</v>
+        <v>6.037251655629141</v>
       </c>
       <c r="AK3">
-        <v>2.71973587674248</v>
+        <v>13.6829268292683</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bank of Jordan (ASE:BOJX)</t>
+          <t>The Housing Bank for Trade and Finance (ASE:THBK)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0251</v>
+        <v>0.0101</v>
       </c>
       <c r="E4">
-        <v>0.0549</v>
+        <v>0.0144</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,28 +850,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>75.7</v>
+        <v>176.2</v>
       </c>
       <c r="L4">
-        <v>0.3830971659919029</v>
+        <v>0.3613617719442165</v>
       </c>
       <c r="M4">
-        <v>34.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="N4">
-        <v>0.05855161787365178</v>
+        <v>0.05223511978266238</v>
       </c>
       <c r="O4">
-        <v>0.4517833553500661</v>
+        <v>0.4801362088535755</v>
       </c>
       <c r="P4">
-        <v>34.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="Q4">
-        <v>0.05855161787365178</v>
+        <v>0.05223511978266238</v>
       </c>
       <c r="R4">
-        <v>0.4517833553500661</v>
+        <v>0.4801362088535755</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,55 +880,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>532.5</v>
+        <v>1197.3</v>
       </c>
       <c r="V4">
-        <v>0.9116589625064201</v>
+        <v>0.7392566065695233</v>
       </c>
       <c r="W4">
-        <v>0.1262297815574454</v>
+        <v>0.1105187229505112</v>
       </c>
       <c r="X4">
-        <v>0.07228061289073502</v>
+        <v>0.1171508112395169</v>
       </c>
       <c r="Y4">
-        <v>0.05394916866671036</v>
+        <v>-0.006632088289005661</v>
       </c>
       <c r="Z4">
-        <v>1.6731583403895</v>
+        <v>0.6864705054202452</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06876229718950461</v>
+        <v>0.1077330983956633</v>
       </c>
       <c r="AC4">
-        <v>-0.06876229718950461</v>
+        <v>-0.1077330983956633</v>
       </c>
       <c r="AD4">
-        <v>105.7</v>
+        <v>590.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>105.7</v>
+        <v>590.5</v>
       </c>
       <c r="AG4">
-        <v>-426.8</v>
+        <v>-606.8</v>
       </c>
       <c r="AH4">
-        <v>0.1532328211075674</v>
+        <v>0.2671824804307498</v>
       </c>
       <c r="AI4">
-        <v>0.1377916829618042</v>
+        <v>0.2573433278131265</v>
       </c>
       <c r="AJ4">
-        <v>-2.713286713286713</v>
+        <v>-0.59913112164297</v>
       </c>
       <c r="AK4">
-        <v>-1.819266837169651</v>
+        <v>-0.5529937118381482</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -945,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Arab Bank Group (ASE:ARBK)</t>
+          <t>Jordan Ahli Bank (ASE:AHLI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0423</v>
+        <v>-0.00605</v>
       </c>
       <c r="E5">
-        <v>-0.114</v>
+        <v>0.0443</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,28 +972,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>236.6</v>
+        <v>24.6</v>
       </c>
       <c r="L5">
-        <v>0.1603850325379609</v>
+        <v>0.1726315789473684</v>
       </c>
       <c r="M5">
-        <v>111</v>
+        <v>19.8</v>
       </c>
       <c r="N5">
-        <v>0.02510800968128662</v>
+        <v>0.06547619047619048</v>
       </c>
       <c r="O5">
-        <v>0.4691462383770076</v>
+        <v>0.8048780487804877</v>
       </c>
       <c r="P5">
-        <v>111</v>
+        <v>19.8</v>
       </c>
       <c r="Q5">
-        <v>0.02510800968128662</v>
+        <v>0.06547619047619048</v>
       </c>
       <c r="R5">
-        <v>0.4691462383770076</v>
+        <v>0.8048780487804877</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1002,55 +1002,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>14304.1</v>
+        <v>339.4</v>
       </c>
       <c r="V5">
-        <v>3.235562894433261</v>
+        <v>1.122354497354497</v>
       </c>
       <c r="W5">
-        <v>0.02560716914152128</v>
+        <v>0.05406593406593407</v>
       </c>
       <c r="X5">
-        <v>0.0744109127783095</v>
+        <v>0.1432508688943318</v>
       </c>
       <c r="Y5">
-        <v>-0.04880374363678822</v>
+        <v>-0.08918493482839776</v>
       </c>
       <c r="Z5">
-        <v>-0.7100842358604091</v>
+        <v>0.4172767203513909</v>
       </c>
       <c r="AA5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06964849061571785</v>
+        <v>0.1141496154722212</v>
       </c>
       <c r="AC5">
-        <v>-0.06964849061571785</v>
+        <v>-0.1141496154722212</v>
       </c>
       <c r="AD5">
-        <v>1035.7</v>
+        <v>272.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1035.7</v>
+        <v>272.9</v>
       </c>
       <c r="AG5">
-        <v>-13268.4</v>
+        <v>-66.5</v>
       </c>
       <c r="AH5">
-        <v>0.1898068394238171</v>
+        <v>0.4743612028506866</v>
       </c>
       <c r="AI5">
-        <v>0.09070209393363518</v>
+        <v>0.3716464660220618</v>
       </c>
       <c r="AJ5">
-        <v>1.499677875105962</v>
+        <v>-0.2818991097922849</v>
       </c>
       <c r="AK5">
-        <v>4.598461218548556</v>
+        <v>-0.1683970625474804</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Housing Bank for Trade and Finance (ASE:THBK)</t>
+          <t>Capital Bank of Jordan (ASE:CAPL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.04650000000000001</v>
+        <v>0.174</v>
       </c>
       <c r="E6">
-        <v>-0.0926</v>
+        <v>0.447</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1094,28 +1094,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>111.5</v>
+        <v>116.6</v>
       </c>
       <c r="L6">
-        <v>0.2850933265149578</v>
+        <v>0.4774774774774775</v>
       </c>
       <c r="M6">
-        <v>50.7</v>
+        <v>40.9</v>
       </c>
       <c r="N6">
-        <v>0.03083378945447911</v>
+        <v>0.0452383585886517</v>
       </c>
       <c r="O6">
-        <v>0.4547085201793722</v>
+        <v>0.3507718696397942</v>
       </c>
       <c r="P6">
-        <v>50.7</v>
+        <v>40.9</v>
       </c>
       <c r="Q6">
-        <v>0.03083378945447911</v>
+        <v>0.0452383585886517</v>
       </c>
       <c r="R6">
-        <v>0.4547085201793722</v>
+        <v>0.3507718696397942</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1124,55 +1124,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1373.4</v>
+        <v>843.7</v>
       </c>
       <c r="V6">
-        <v>0.8352490421455939</v>
+        <v>0.9331932308372968</v>
       </c>
       <c r="W6">
-        <v>0.07222438139655396</v>
+        <v>0.2469292672596357</v>
       </c>
       <c r="X6">
-        <v>0.0769427777239611</v>
+        <v>0.1521713404861267</v>
       </c>
       <c r="Y6">
-        <v>-0.004718396327407143</v>
+        <v>0.09475792677350903</v>
       </c>
       <c r="Z6">
-        <v>0.6164880201765449</v>
+        <v>0.5147554806070825</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.07060703449620839</v>
+        <v>0.1155840429218509</v>
       </c>
       <c r="AC6">
-        <v>-0.07060703449620839</v>
+        <v>-0.1155840429218509</v>
       </c>
       <c r="AD6">
-        <v>489.4</v>
+        <v>982.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>489.4</v>
+        <v>982.1</v>
       </c>
       <c r="AG6">
-        <v>-884.0000000000001</v>
+        <v>138.4</v>
       </c>
       <c r="AH6">
-        <v>0.2293668275765103</v>
+        <v>0.5206764924186195</v>
       </c>
       <c r="AI6">
-        <v>0.2255091696617823</v>
+        <v>0.5220048899755501</v>
       </c>
       <c r="AJ6">
-        <v>-1.162698934631067</v>
+        <v>0.132757793764988</v>
       </c>
       <c r="AK6">
-        <v>-1.109437751004017</v>
+        <v>0.1333718801194951</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arab Jordan Investment Bank (ASE:AJIB)</t>
+          <t>Jordan Commercial Bank (ASE:JCBK)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0323</v>
+        <v>-0.0004</v>
       </c>
       <c r="E7">
-        <v>-0.0732</v>
+        <v>0.0395</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1216,85 +1216,82 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>20.3</v>
+        <v>14.8</v>
       </c>
       <c r="L7">
-        <v>0.2678100263852243</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="M7">
-        <v>21.2</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.07104557640750671</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>1.044334975369458</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>21.2</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.07104557640750671</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>1.044334975369458</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>402.1</v>
+        <v>63</v>
       </c>
       <c r="V7">
-        <v>1.347520107238606</v>
+        <v>0.3727810650887574</v>
       </c>
       <c r="W7">
-        <v>0.07073170731707318</v>
+        <v>0.07344913151364765</v>
       </c>
       <c r="X7">
-        <v>0.07797202277413086</v>
+        <v>0.1664191296062343</v>
       </c>
       <c r="Y7">
-        <v>-0.007240315457057681</v>
+        <v>-0.0929699980925866</v>
       </c>
       <c r="Z7">
-        <v>0.6295681063122924</v>
+        <v>0.245511319281811</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.07097045829402643</v>
+        <v>0.1174154946527229</v>
       </c>
       <c r="AC7">
-        <v>-0.07097045829402643</v>
+        <v>-0.1174154946527229</v>
       </c>
       <c r="AD7">
-        <v>96.5</v>
+        <v>233.2</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>96.5</v>
+        <v>233.2</v>
       </c>
       <c r="AG7">
-        <v>-305.6</v>
+        <v>170.2</v>
       </c>
       <c r="AH7">
-        <v>0.2443656621929603</v>
+        <v>0.5798110392839383</v>
       </c>
       <c r="AI7">
-        <v>0.2330917874396135</v>
+        <v>0.5132042253521126</v>
       </c>
       <c r="AJ7">
-        <v>42.44444444444418</v>
+        <v>0.5017688679245282</v>
       </c>
       <c r="AK7">
-        <v>-25.68067226890761</v>
+        <v>0.4348492590700051</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1311,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bank al Etihad (ASE:UBSI)</t>
+          <t>Invest Bank (ASE:INVB)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1320,10 +1317,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.105</v>
+        <v>0.0437</v>
       </c>
       <c r="E8">
-        <v>-0.0169</v>
+        <v>0.075</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1338,28 +1335,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>42.4</v>
+        <v>26.6</v>
       </c>
       <c r="L8">
-        <v>0.1861281826163301</v>
+        <v>0.3247863247863248</v>
       </c>
       <c r="M8">
-        <v>25.9</v>
+        <v>14.1</v>
       </c>
       <c r="N8">
-        <v>0.06556962025316455</v>
+        <v>0.06459001374255612</v>
       </c>
       <c r="O8">
-        <v>0.6108490566037735</v>
+        <v>0.5300751879699248</v>
       </c>
       <c r="P8">
-        <v>25.9</v>
+        <v>14.1</v>
       </c>
       <c r="Q8">
-        <v>0.06556962025316455</v>
+        <v>0.06459001374255612</v>
       </c>
       <c r="R8">
-        <v>0.6108490566037735</v>
+        <v>0.5300751879699248</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1368,55 +1365,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>1721.5</v>
+        <v>127.4</v>
       </c>
       <c r="V8">
-        <v>4.358227848101266</v>
+        <v>0.5836005497022446</v>
       </c>
       <c r="W8">
-        <v>0.0748059280169372</v>
+        <v>0.1045186640471513</v>
       </c>
       <c r="X8">
-        <v>0.08597004312930882</v>
+        <v>0.1726148439813172</v>
       </c>
       <c r="Y8">
-        <v>-0.01116411511237163</v>
+        <v>-0.06809617993416596</v>
       </c>
       <c r="Z8">
-        <v>-0.4722222222222222</v>
+        <v>0.242092817026308</v>
       </c>
       <c r="AA8">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.07337578621817066</v>
+        <v>0.118078107116582</v>
       </c>
       <c r="AC8">
-        <v>-0.07337578621817066</v>
+        <v>-0.118078107116582</v>
       </c>
       <c r="AD8">
-        <v>206.8</v>
+        <v>329.1</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>206.8</v>
+        <v>329.1</v>
       </c>
       <c r="AG8">
-        <v>-1514.7</v>
+        <v>201.7</v>
       </c>
       <c r="AH8">
-        <v>0.3436357593885012</v>
+        <v>0.6012056996711728</v>
       </c>
       <c r="AI8">
-        <v>0.2205866666666667</v>
+        <v>0.5510716677829872</v>
       </c>
       <c r="AJ8">
-        <v>1.352773064213629</v>
+        <v>0.4802380952380953</v>
       </c>
       <c r="AK8">
-        <v>1.932015306122449</v>
+        <v>0.4293316304810557</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1433,7 +1430,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jordan Commercial Bank (ASE:JCBK)</t>
+          <t>Cairo Amman Bank (ASE:CABK)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1442,10 +1439,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.0128</v>
+        <v>0.0317</v>
       </c>
       <c r="E9">
-        <v>-0.0915</v>
+        <v>0.0319</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1460,82 +1457,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>6.78</v>
+        <v>47.2</v>
       </c>
       <c r="L9">
-        <v>0.1296367112810708</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>24.1</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.06720580033463469</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0.510593220338983</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>24.1</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.06720580033463469</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.510593220338983</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>101.6</v>
+        <v>502.3</v>
       </c>
       <c r="V9">
-        <v>0.5825688073394495</v>
+        <v>1.400725041829336</v>
       </c>
       <c r="W9">
-        <v>0.03480492813141683</v>
+        <v>0.08892238131122834</v>
       </c>
       <c r="X9">
-        <v>0.1008618225555708</v>
+        <v>0.1743049590539204</v>
       </c>
       <c r="Y9">
-        <v>-0.06605689442415398</v>
+        <v>-0.08538257774269206</v>
       </c>
       <c r="Z9">
-        <v>0.2819407008086253</v>
+        <v>0.3831900668576886</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.0765014264162597</v>
+        <v>0.1182473062674951</v>
       </c>
       <c r="AC9">
-        <v>-0.0765014264162597</v>
+        <v>-0.1182473062674951</v>
       </c>
       <c r="AD9">
-        <v>156.3</v>
+        <v>553.1</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>156.3</v>
+        <v>553.1</v>
       </c>
       <c r="AG9">
-        <v>54.70000000000002</v>
+        <v>50.80000000000001</v>
       </c>
       <c r="AH9">
-        <v>0.4726338070758996</v>
+        <v>0.606668860370736</v>
       </c>
       <c r="AI9">
-        <v>0.4368362213527111</v>
+        <v>0.4892525431225122</v>
       </c>
       <c r="AJ9">
-        <v>0.238760366652117</v>
+        <v>0.1240840254030288</v>
       </c>
       <c r="AK9">
-        <v>0.2135050741608119</v>
+        <v>0.08086596625278575</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jordan Ahli Bank (ASE:AHLI)</t>
+          <t>Jordan Kuwait Bank (ASE:JOKB)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.0137</v>
+        <v>0.00153</v>
       </c>
       <c r="E10">
-        <v>-0.0288</v>
+        <v>-0.119</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1579,28 +1579,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>14.8</v>
+        <v>20.4</v>
       </c>
       <c r="L10">
-        <v>0.1117824773413897</v>
+        <v>0.1376518218623482</v>
       </c>
       <c r="M10">
-        <v>11.3</v>
+        <v>0.113</v>
       </c>
       <c r="N10">
-        <v>0.04115076474872542</v>
+        <v>0.0003241537578886976</v>
       </c>
       <c r="O10">
-        <v>0.7635135135135135</v>
+        <v>0.00553921568627451</v>
       </c>
       <c r="P10">
-        <v>11.3</v>
+        <v>0.113</v>
       </c>
       <c r="Q10">
-        <v>0.04115076474872542</v>
+        <v>0.0003241537578886976</v>
       </c>
       <c r="R10">
-        <v>0.7635135135135135</v>
+        <v>0.00553921568627451</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1609,55 +1609,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>439.6</v>
+        <v>826.7</v>
       </c>
       <c r="V10">
-        <v>1.600873998543336</v>
+        <v>2.371485943775101</v>
       </c>
       <c r="W10">
-        <v>0.03315412186379928</v>
+        <v>0.03117359413202934</v>
       </c>
       <c r="X10">
-        <v>0.1040194710991298</v>
+        <v>0.150295565690247</v>
       </c>
       <c r="Y10">
-        <v>-0.07086534923533055</v>
+        <v>-0.1191219715582177</v>
       </c>
       <c r="Z10">
-        <v>0.4067588325652842</v>
+        <v>0.3581440309328178</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.07701262791509265</v>
+        <v>0.1200107765873641</v>
       </c>
       <c r="AC10">
-        <v>-0.07701262791509265</v>
+        <v>-0.1200107765873641</v>
       </c>
       <c r="AD10">
-        <v>267.8</v>
+        <v>365.2</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>267.8</v>
+        <v>365.2</v>
       </c>
       <c r="AG10">
-        <v>-171.8</v>
+        <v>-461.5000000000001</v>
       </c>
       <c r="AH10">
-        <v>0.4937315634218288</v>
+        <v>0.5116279069767442</v>
       </c>
       <c r="AI10">
-        <v>0.3694812362030905</v>
+        <v>0.3563274465801541</v>
       </c>
       <c r="AJ10">
-        <v>-1.671206225680934</v>
+        <v>4.087688219663418</v>
       </c>
       <c r="AK10">
-        <v>-0.6023842917251052</v>
+        <v>-2.328456104944501</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.0526</v>
+        <v>-0.036</v>
       </c>
       <c r="E11">
-        <v>-0.136</v>
+        <v>-0.135</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1701,28 +1701,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>10.5</v>
+        <v>8.48</v>
       </c>
       <c r="L11">
-        <v>0.2075098814229249</v>
+        <v>0.1692614770459082</v>
       </c>
       <c r="M11">
-        <v>0.037</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="N11">
-        <v>0.0002708638360175696</v>
+        <v>0.07435483870967742</v>
       </c>
       <c r="O11">
-        <v>0.003523809523809524</v>
+        <v>1.087264150943396</v>
       </c>
       <c r="P11">
-        <v>0.037</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="Q11">
-        <v>0.0002708638360175696</v>
+        <v>0.07435483870967742</v>
       </c>
       <c r="R11">
-        <v>0.003523809523809524</v>
+        <v>1.087264150943396</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1731,667 +1731,60 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>117.7</v>
+        <v>172</v>
       </c>
       <c r="V11">
-        <v>0.8616398243045389</v>
+        <v>1.387096774193548</v>
       </c>
       <c r="W11">
-        <v>0.04654255319148936</v>
+        <v>0.03603909902252444</v>
       </c>
       <c r="X11">
-        <v>0.1041314121777151</v>
+        <v>0.167199732101349</v>
       </c>
       <c r="Y11">
-        <v>-0.05758885898622574</v>
+        <v>-0.1311606330788245</v>
       </c>
       <c r="Z11">
-        <v>0.2373358348968105</v>
+        <v>0.1994426751592357</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.07703000075768134</v>
+        <v>0.1228630812558658</v>
       </c>
       <c r="AC11">
-        <v>-0.07703000075768134</v>
+        <v>-0.1228630812558658</v>
       </c>
       <c r="AD11">
-        <v>133.6</v>
+        <v>173.1</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>133.6</v>
+        <v>173.1</v>
       </c>
       <c r="AG11">
-        <v>15.89999999999999</v>
+        <v>1.099999999999994</v>
       </c>
       <c r="AH11">
-        <v>0.4944485566247224</v>
+        <v>0.5826321104005385</v>
       </c>
       <c r="AI11">
-        <v>0.3621577663323394</v>
+        <v>0.4319940104816571</v>
       </c>
       <c r="AJ11">
-        <v>0.1042622950819672</v>
+        <v>0.008792965627497956</v>
       </c>
       <c r="AK11">
-        <v>0.06329617834394902</v>
+        <v>0.004809794490599014</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Capital Bank of Jordan (ASE:EXFB)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>0.06059999999999999</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>81.8</v>
-      </c>
-      <c r="L12">
-        <v>0.5308241401687216</v>
-      </c>
-      <c r="M12">
-        <v>40.08</v>
-      </c>
-      <c r="N12">
-        <v>0.06997206703910615</v>
-      </c>
-      <c r="O12">
-        <v>0.4899755501222494</v>
-      </c>
-      <c r="P12">
-        <v>33.9</v>
-      </c>
-      <c r="Q12">
-        <v>0.05918296089385475</v>
-      </c>
-      <c r="R12">
-        <v>0.4144254278728606</v>
-      </c>
-      <c r="S12">
-        <v>6.18</v>
-      </c>
-      <c r="T12">
-        <v>0.1541916167664671</v>
-      </c>
-      <c r="U12">
-        <v>630</v>
-      </c>
-      <c r="V12">
-        <v>1.099860335195531</v>
-      </c>
-      <c r="W12">
-        <v>0.1872281986724651</v>
-      </c>
-      <c r="X12">
-        <v>0.1091528518744624</v>
-      </c>
-      <c r="Y12">
-        <v>0.07807534679800265</v>
-      </c>
-      <c r="Z12">
-        <v>0.2910842463165847</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0.0777617204774472</v>
-      </c>
-      <c r="AC12">
-        <v>-0.0777617204774472</v>
-      </c>
-      <c r="AD12">
-        <v>632.2</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>632.2</v>
-      </c>
-      <c r="AG12">
-        <v>2.200000000000045</v>
-      </c>
-      <c r="AH12">
-        <v>0.5246473029045644</v>
-      </c>
-      <c r="AI12">
-        <v>0.5378594521014123</v>
-      </c>
-      <c r="AJ12">
-        <v>0.003826086956521818</v>
-      </c>
-      <c r="AK12">
-        <v>0.004033736707004116</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Société Générale de Banque - Jordanie (ASE:SGBJ)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>-0.00595</v>
-      </c>
-      <c r="E13">
-        <v>-0.113</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>7</v>
-      </c>
-      <c r="L13">
-        <v>0.1994301994301994</v>
-      </c>
-      <c r="M13">
-        <v>11.3</v>
-      </c>
-      <c r="N13">
-        <v>0.05721518987341773</v>
-      </c>
-      <c r="O13">
-        <v>1.614285714285714</v>
-      </c>
-      <c r="P13">
-        <v>11.3</v>
-      </c>
-      <c r="Q13">
-        <v>0.05721518987341773</v>
-      </c>
-      <c r="R13">
-        <v>1.614285714285714</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>70.2</v>
-      </c>
-      <c r="V13">
-        <v>0.3554430379746836</v>
-      </c>
-      <c r="W13">
-        <v>0.03475670307845084</v>
-      </c>
-      <c r="X13">
-        <v>0.09604592107617793</v>
-      </c>
-      <c r="Y13">
-        <v>-0.06128921799772709</v>
-      </c>
-      <c r="Z13">
-        <v>0.1363636363636364</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0.0783126999596387</v>
-      </c>
-      <c r="AC13">
-        <v>-0.0783126999596387</v>
-      </c>
-      <c r="AD13">
-        <v>153.2</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>153.2</v>
-      </c>
-      <c r="AG13">
-        <v>82.99999999999999</v>
-      </c>
-      <c r="AH13">
-        <v>0.4368406045052751</v>
-      </c>
-      <c r="AI13">
-        <v>0.4058278145695364</v>
-      </c>
-      <c r="AJ13">
-        <v>0.2959001782531194</v>
-      </c>
-      <c r="AK13">
-        <v>0.2700943703221607</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Jordan Kuwait Bank (ASE:JOKB)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>-0.08599999999999999</v>
-      </c>
-      <c r="E14">
-        <v>-0.361</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>5.46</v>
-      </c>
-      <c r="L14">
-        <v>0.05565749235474007</v>
-      </c>
-      <c r="M14">
-        <v>0.007</v>
-      </c>
-      <c r="N14">
-        <v>2.432244614315497e-05</v>
-      </c>
-      <c r="O14">
-        <v>0.001282051282051282</v>
-      </c>
-      <c r="P14">
-        <v>0.007</v>
-      </c>
-      <c r="Q14">
-        <v>2.432244614315497e-05</v>
-      </c>
-      <c r="R14">
-        <v>0.001282051282051282</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>604.2</v>
-      </c>
-      <c r="V14">
-        <v>2.099374565670605</v>
-      </c>
-      <c r="W14">
-        <v>0.008502024291497975</v>
-      </c>
-      <c r="X14">
-        <v>0.1155334430698043</v>
-      </c>
-      <c r="Y14">
-        <v>-0.1070314187783063</v>
-      </c>
-      <c r="Z14">
-        <v>0.4048699958728847</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0.07857427985880917</v>
-      </c>
-      <c r="AC14">
-        <v>-0.07857427985880917</v>
-      </c>
-      <c r="AD14">
-        <v>363.6</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>363.6</v>
-      </c>
-      <c r="AG14">
-        <v>-240.6</v>
-      </c>
-      <c r="AH14">
-        <v>0.5581823764200183</v>
-      </c>
-      <c r="AI14">
-        <v>0.3569955817378498</v>
-      </c>
-      <c r="AJ14">
-        <v>-5.097457627118645</v>
-      </c>
-      <c r="AK14">
-        <v>-0.5807385952208546</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Cairo Amman Bank (ASE:CABK)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>0.00392</v>
-      </c>
-      <c r="E15">
-        <v>-0.0486</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>41.5</v>
-      </c>
-      <c r="L15">
-        <v>0.226528384279476</v>
-      </c>
-      <c r="M15">
-        <v>32.2</v>
-      </c>
-      <c r="N15">
-        <v>0.08641975308641976</v>
-      </c>
-      <c r="O15">
-        <v>0.7759036144578314</v>
-      </c>
-      <c r="P15">
-        <v>32.2</v>
-      </c>
-      <c r="Q15">
-        <v>0.08641975308641976</v>
-      </c>
-      <c r="R15">
-        <v>0.7759036144578314</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>481.8</v>
-      </c>
-      <c r="V15">
-        <v>1.293075684380032</v>
-      </c>
-      <c r="W15">
-        <v>0.08230860769535898</v>
-      </c>
-      <c r="X15">
-        <v>0.1159372856595398</v>
-      </c>
-      <c r="Y15">
-        <v>-0.03362867796418083</v>
-      </c>
-      <c r="Z15">
-        <v>0.302210491586935</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0.07862186797499335</v>
-      </c>
-      <c r="AC15">
-        <v>-0.07862186797499335</v>
-      </c>
-      <c r="AD15">
-        <v>474.5</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>474.5</v>
-      </c>
-      <c r="AG15">
-        <v>-7.300000000000011</v>
-      </c>
-      <c r="AH15">
-        <v>0.5601463817731083</v>
-      </c>
-      <c r="AI15">
-        <v>0.4652416903618002</v>
-      </c>
-      <c r="AJ15">
-        <v>-0.01998357514371752</v>
-      </c>
-      <c r="AK15">
-        <v>-0.01356625162609183</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Invest Bank (ASE:INVB)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>-0.00038</v>
-      </c>
-      <c r="E16">
-        <v>-0.0316</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>17.3</v>
-      </c>
-      <c r="L16">
-        <v>0.2694704049844237</v>
-      </c>
-      <c r="M16">
-        <v>16.9</v>
-      </c>
-      <c r="N16">
-        <v>0.08203883495145631</v>
-      </c>
-      <c r="O16">
-        <v>0.9768786127167629</v>
-      </c>
-      <c r="P16">
-        <v>16.9</v>
-      </c>
-      <c r="Q16">
-        <v>0.08203883495145631</v>
-      </c>
-      <c r="R16">
-        <v>0.9768786127167629</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>202.8</v>
-      </c>
-      <c r="V16">
-        <v>0.9844660194174758</v>
-      </c>
-      <c r="W16">
-        <v>0.06760453302071122</v>
-      </c>
-      <c r="X16">
-        <v>0.1206436625337338</v>
-      </c>
-      <c r="Y16">
-        <v>-0.05303912951302259</v>
-      </c>
-      <c r="Z16">
-        <v>0.1687253613666229</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0.0791467997641524</v>
-      </c>
-      <c r="AC16">
-        <v>-0.0791467997641524</v>
-      </c>
-      <c r="AD16">
-        <v>286.6</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>286.6</v>
-      </c>
-      <c r="AG16">
-        <v>83.80000000000001</v>
-      </c>
-      <c r="AH16">
-        <v>0.5818107998375964</v>
-      </c>
-      <c r="AI16">
-        <v>0.5253895508707608</v>
-      </c>
-      <c r="AJ16">
-        <v>0.2891649413388544</v>
-      </c>
-      <c r="AK16">
-        <v>0.2445287423402393</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/jordan/jordan_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ11"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0101</v>
+        <v>0.0507</v>
       </c>
       <c r="E2">
-        <v>0.0319</v>
+        <v>0.05325</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.0001016574312000622</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>7.200850277268352e-05</v>
       </c>
       <c r="K2">
-        <v>487.68</v>
+        <v>529.1999999999999</v>
       </c>
       <c r="L2">
-        <v>0.3031893068075847</v>
+        <v>0.308535447761194</v>
       </c>
       <c r="M2">
-        <v>243.633</v>
+        <v>283.03</v>
       </c>
       <c r="N2">
-        <v>0.05235928735681588</v>
+        <v>0.0691582162492364</v>
       </c>
       <c r="O2">
-        <v>0.4995755413385826</v>
+        <v>0.5348261526832956</v>
       </c>
       <c r="P2">
-        <v>243.633</v>
+        <v>283.03</v>
       </c>
       <c r="Q2">
-        <v>0.05235928735681588</v>
+        <v>0.0691582162492364</v>
       </c>
       <c r="R2">
-        <v>0.4995755413385826</v>
+        <v>0.5348261526832956</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,61 +636,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4888.1</v>
+        <v>5962.8</v>
       </c>
       <c r="V2">
-        <v>1.050503965098536</v>
+        <v>1.457006719609041</v>
       </c>
       <c r="W2">
-        <v>0.0813183428307408</v>
+        <v>0.1075167732475673</v>
       </c>
       <c r="X2">
-        <v>0.1521713404861267</v>
+        <v>0.1233603461683043</v>
       </c>
       <c r="Y2">
-        <v>-0.07085299765538591</v>
+        <v>-0.01584357292073701</v>
       </c>
       <c r="Z2">
-        <v>0.4554463855933403</v>
+        <v>0.4293911443051862</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1174154946527229</v>
+        <v>0.09835632209430797</v>
       </c>
       <c r="AC2">
-        <v>-0.1174154946527229</v>
+        <v>-0.09820878236879946</v>
       </c>
       <c r="AD2">
-        <v>3586.2</v>
+        <v>3213.9</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.1931858700282665</v>
       </c>
       <c r="AF2">
-        <v>3586.2</v>
+        <v>3214.093185870028</v>
       </c>
       <c r="AG2">
-        <v>-1301.900000000001</v>
+        <v>-2748.706814129972</v>
       </c>
       <c r="AH2">
-        <v>0.4352554221839234</v>
+        <v>0.4398894401409475</v>
       </c>
       <c r="AI2">
-        <v>0.3864023273354164</v>
+        <v>0.3687538805895869</v>
       </c>
       <c r="AJ2">
-        <v>-0.3884877058963955</v>
+        <v>-2.045483518619231</v>
       </c>
       <c r="AK2">
-        <v>-0.2963645883129597</v>
+        <v>-0.9983342232626755</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>15088.7323943662</v>
+      </c>
+      <c r="AP2">
+        <v>-12904.72682690128</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bank of Jordan (ASE:BOJX)</t>
+          <t>Arab Jordan Investment Bank (ASE:AJIB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0182</v>
+        <v>0.0302</v>
       </c>
       <c r="E3">
-        <v>-0.058</v>
+        <v>0.0489</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>52.8</v>
+        <v>27.6</v>
       </c>
       <c r="L3">
-        <v>0.2771653543307087</v>
+        <v>0.3</v>
       </c>
       <c r="M3">
-        <v>50.8</v>
+        <v>39.1</v>
       </c>
       <c r="N3">
-        <v>0.08348397699260476</v>
+        <v>0.1423889293517844</v>
       </c>
       <c r="O3">
-        <v>0.9621212121212122</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="P3">
-        <v>50.8</v>
+        <v>39.1</v>
       </c>
       <c r="Q3">
-        <v>0.08348397699260476</v>
+        <v>0.1423889293517844</v>
       </c>
       <c r="R3">
-        <v>0.9621212121212122</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>816.3</v>
+        <v>326.4</v>
       </c>
       <c r="V3">
-        <v>1.341495480690222</v>
+        <v>1.188638018936635</v>
       </c>
       <c r="W3">
-        <v>0.0813183428307408</v>
+        <v>0.0909690177982861</v>
       </c>
       <c r="X3">
-        <v>0.1063962723671002</v>
+        <v>0.09145381495502189</v>
       </c>
       <c r="Y3">
-        <v>-0.02507792953635939</v>
+        <v>-0.0004847971567357862</v>
       </c>
       <c r="Z3">
-        <v>0.8561797752808988</v>
+        <v>0.9010773751224288</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.103332358334463</v>
+        <v>0.0896031678807067</v>
       </c>
       <c r="AC3">
-        <v>-0.103332358334463</v>
+        <v>-0.0896031678807067</v>
       </c>
       <c r="AD3">
-        <v>87</v>
+        <v>67.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>87</v>
+        <v>67.3</v>
       </c>
       <c r="AG3">
-        <v>-729.3</v>
+        <v>-259.1</v>
       </c>
       <c r="AH3">
-        <v>0.1250898634076204</v>
+        <v>0.1968411816320561</v>
       </c>
       <c r="AI3">
-        <v>0.1140235910878113</v>
+        <v>0.1759937238493724</v>
       </c>
       <c r="AJ3">
-        <v>6.037251655629141</v>
+        <v>-16.716129032258</v>
       </c>
       <c r="AK3">
-        <v>13.6829268292683</v>
+        <v>-4.626785714285709</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,10 +838,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0101</v>
+        <v>0.0578</v>
       </c>
       <c r="E4">
-        <v>0.0144</v>
+        <v>0.0555</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,28 +856,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>176.2</v>
+        <v>203.1</v>
       </c>
       <c r="L4">
-        <v>0.3613617719442165</v>
+        <v>0.3460555460896235</v>
       </c>
       <c r="M4">
-        <v>84.59999999999999</v>
+        <v>105.7</v>
       </c>
       <c r="N4">
-        <v>0.05223511978266238</v>
+        <v>0.06388250936782304</v>
       </c>
       <c r="O4">
-        <v>0.4801362088535755</v>
+        <v>0.5204332840965042</v>
       </c>
       <c r="P4">
-        <v>84.59999999999999</v>
+        <v>105.7</v>
       </c>
       <c r="Q4">
-        <v>0.05223511978266238</v>
+        <v>0.06388250936782304</v>
       </c>
       <c r="R4">
-        <v>0.4801362088535755</v>
+        <v>0.5204332840965042</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,55 +886,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1197.3</v>
+        <v>1050.9</v>
       </c>
       <c r="V4">
-        <v>0.7392566065695233</v>
+        <v>0.6351384020307024</v>
       </c>
       <c r="W4">
-        <v>0.1105187229505112</v>
+        <v>0.1248233052670395</v>
       </c>
       <c r="X4">
-        <v>0.1171508112395169</v>
+        <v>0.09330101118284784</v>
       </c>
       <c r="Y4">
-        <v>-0.006632088289005661</v>
+        <v>0.03152229408419169</v>
       </c>
       <c r="Z4">
-        <v>0.6864705054202452</v>
+        <v>0.5752229736352054</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1077330983956633</v>
+        <v>0.09072155011772418</v>
       </c>
       <c r="AC4">
-        <v>-0.1077330983956633</v>
+        <v>-0.09072155011772418</v>
       </c>
       <c r="AD4">
-        <v>590.5</v>
+        <v>492.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>590.5</v>
+        <v>492.3</v>
       </c>
       <c r="AG4">
-        <v>-606.8</v>
+        <v>-558.6000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.2671824804307498</v>
+        <v>0.2293073734221436</v>
       </c>
       <c r="AI4">
-        <v>0.2573433278131265</v>
+        <v>0.2131814835664487</v>
       </c>
       <c r="AJ4">
-        <v>-0.59913112164297</v>
+        <v>-0.5096715328467155</v>
       </c>
       <c r="AK4">
-        <v>-0.5529937118381482</v>
+        <v>-0.4438970120788304</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -945,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jordan Ahli Bank (ASE:AHLI)</t>
+          <t>Jordan Kuwait Bank (ASE:JOKB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -954,10 +960,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.00605</v>
+        <v>0.08349999999999999</v>
       </c>
       <c r="E5">
-        <v>0.0443</v>
+        <v>0.125</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,28 +978,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>24.6</v>
+        <v>82.8</v>
       </c>
       <c r="L5">
-        <v>0.1726315789473684</v>
+        <v>0.3166347992351816</v>
       </c>
       <c r="M5">
-        <v>19.8</v>
+        <v>17.1</v>
       </c>
       <c r="N5">
-        <v>0.06547619047619048</v>
+        <v>0.03149751335420888</v>
       </c>
       <c r="O5">
-        <v>0.8048780487804877</v>
+        <v>0.2065217391304348</v>
       </c>
       <c r="P5">
-        <v>19.8</v>
+        <v>17.1</v>
       </c>
       <c r="Q5">
-        <v>0.06547619047619048</v>
+        <v>0.03149751335420888</v>
       </c>
       <c r="R5">
-        <v>0.8048780487804877</v>
+        <v>0.2065217391304348</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1002,55 +1008,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>339.4</v>
+        <v>2070.9</v>
       </c>
       <c r="V5">
-        <v>1.122354497354497</v>
+        <v>3.81451464358077</v>
       </c>
       <c r="W5">
-        <v>0.05406593406593407</v>
+        <v>0.1259698767685988</v>
       </c>
       <c r="X5">
-        <v>0.1432508688943318</v>
+        <v>0.1229900201237882</v>
       </c>
       <c r="Y5">
-        <v>-0.08918493482839776</v>
+        <v>0.002979856644810583</v>
       </c>
       <c r="Z5">
-        <v>0.4172767203513909</v>
+        <v>1.335546475995915</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.1141496154722212</v>
+        <v>0.09756198826000576</v>
       </c>
       <c r="AC5">
-        <v>-0.1141496154722212</v>
+        <v>-0.09756198826000576</v>
       </c>
       <c r="AD5">
-        <v>272.9</v>
+        <v>619.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>272.9</v>
+        <v>619.2</v>
       </c>
       <c r="AG5">
-        <v>-66.5</v>
+        <v>-1451.7</v>
       </c>
       <c r="AH5">
-        <v>0.4743612028506866</v>
+        <v>0.5328285001290768</v>
       </c>
       <c r="AI5">
-        <v>0.3716464660220618</v>
+        <v>0.3847157502329916</v>
       </c>
       <c r="AJ5">
-        <v>-0.2818991097922849</v>
+        <v>1.597381161971831</v>
       </c>
       <c r="AK5">
-        <v>-0.1683970625474804</v>
+        <v>3.146293888166449</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital Bank of Jordan (ASE:CAPL)</t>
+          <t>Jordan Commercial Bank (ASE:JCBK)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,10 +1082,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.174</v>
+        <v>0.0436</v>
       </c>
       <c r="E6">
-        <v>0.447</v>
+        <v>0.324</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1088,34 +1094,34 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.002618060450365566</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>0.001735001536164394</v>
       </c>
       <c r="K6">
-        <v>116.6</v>
+        <v>16.2</v>
       </c>
       <c r="L6">
-        <v>0.4774774774774775</v>
+        <v>0.2432432432432433</v>
       </c>
       <c r="M6">
-        <v>40.9</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="N6">
-        <v>0.0452383585886517</v>
+        <v>0.049502050380785</v>
       </c>
       <c r="O6">
-        <v>0.3507718696397942</v>
+        <v>0.5216049382716049</v>
       </c>
       <c r="P6">
-        <v>40.9</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q6">
-        <v>0.0452383585886517</v>
+        <v>0.049502050380785</v>
       </c>
       <c r="R6">
-        <v>0.3507718696397942</v>
+        <v>0.5216049382716049</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1124,61 +1130,67 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>843.7</v>
+        <v>88.2</v>
       </c>
       <c r="V6">
-        <v>0.9331932308372968</v>
+        <v>0.5166959578207382</v>
       </c>
       <c r="W6">
-        <v>0.2469292672596357</v>
+        <v>0.07323688969258589</v>
       </c>
       <c r="X6">
-        <v>0.1521713404861267</v>
+        <v>0.1111687372560958</v>
       </c>
       <c r="Y6">
-        <v>0.09475792677350903</v>
+        <v>-0.0379318475635099</v>
       </c>
       <c r="Z6">
-        <v>0.5147554806070825</v>
+        <v>0.1700744609537329</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>0.0002950794510170578</v>
       </c>
       <c r="AB6">
-        <v>0.1155840429218509</v>
+        <v>0.09818425915551555</v>
       </c>
       <c r="AC6">
-        <v>-0.1155840429218509</v>
+        <v>-0.09788917970449849</v>
       </c>
       <c r="AD6">
-        <v>982.1</v>
+        <v>137.2</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>0.1931858700282665</v>
       </c>
       <c r="AF6">
-        <v>982.1</v>
+        <v>137.3931858700282</v>
       </c>
       <c r="AG6">
-        <v>138.4</v>
+        <v>49.19318587002824</v>
       </c>
       <c r="AH6">
-        <v>0.5206764924186195</v>
+        <v>0.4459468504051522</v>
       </c>
       <c r="AI6">
-        <v>0.5220048899755501</v>
+        <v>0.3714401646704165</v>
       </c>
       <c r="AJ6">
-        <v>0.132757793764988</v>
+        <v>0.2237140076687267</v>
       </c>
       <c r="AK6">
-        <v>0.1333718801194951</v>
+        <v>0.1746339220740885</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
         <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>644.131455399061</v>
+      </c>
+      <c r="AP6">
+        <v>230.9539242724331</v>
       </c>
     </row>
     <row r="7">
@@ -1189,7 +1201,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jordan Commercial Bank (ASE:JCBK)</t>
+          <t>Cairo Amman Bank (ASE:CABK)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1198,10 +1210,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0004</v>
+        <v>0.0359</v>
       </c>
       <c r="E7">
-        <v>0.0395</v>
+        <v>0.0373</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1216,82 +1228,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>14.8</v>
+        <v>52</v>
       </c>
       <c r="L7">
-        <v>0.2352941176470588</v>
+        <v>0.2478551000953289</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>26.8</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.0736466062104974</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.5153846153846154</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>26.8</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.0736466062104974</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.5153846153846154</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>63</v>
+        <v>410.6</v>
       </c>
       <c r="V7">
-        <v>0.3727810650887574</v>
+        <v>1.128331959329486</v>
       </c>
       <c r="W7">
-        <v>0.07344913151364765</v>
+        <v>0.09475218658892129</v>
       </c>
       <c r="X7">
-        <v>0.1664191296062343</v>
+        <v>0.1290829452346946</v>
       </c>
       <c r="Y7">
-        <v>-0.0929699980925866</v>
+        <v>-0.03433075864577334</v>
       </c>
       <c r="Z7">
-        <v>0.245511319281811</v>
+        <v>0.3498999332888592</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.1174154946527229</v>
+        <v>0.09852838503310041</v>
       </c>
       <c r="AC7">
-        <v>-0.1174154946527229</v>
+        <v>-0.09852838503310041</v>
       </c>
       <c r="AD7">
-        <v>233.2</v>
+        <v>478</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>233.2</v>
+        <v>478</v>
       </c>
       <c r="AG7">
-        <v>170.2</v>
+        <v>67.39999999999998</v>
       </c>
       <c r="AH7">
-        <v>0.5798110392839383</v>
+        <v>0.5677633923268797</v>
       </c>
       <c r="AI7">
-        <v>0.5132042253521126</v>
+        <v>0.42881492778326</v>
       </c>
       <c r="AJ7">
-        <v>0.5017688679245282</v>
+        <v>0.156271736610248</v>
       </c>
       <c r="AK7">
-        <v>0.4348492590700051</v>
+        <v>0.09572503905695211</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1308,7 +1323,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Invest Bank (ASE:INVB)</t>
+          <t>Capital Bank of Jordan (ASE:CAPL)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1317,10 +1332,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0437</v>
+        <v>0.314</v>
       </c>
       <c r="E8">
-        <v>0.075</v>
+        <v>0.214</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1335,28 +1350,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>26.6</v>
+        <v>102.6</v>
       </c>
       <c r="L8">
-        <v>0.3247863247863248</v>
+        <v>0.2966175195143105</v>
       </c>
       <c r="M8">
-        <v>14.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="N8">
-        <v>0.06459001374255612</v>
+        <v>0.08680693396850601</v>
       </c>
       <c r="O8">
-        <v>0.5300751879699248</v>
+        <v>0.6393762183235867</v>
       </c>
       <c r="P8">
-        <v>14.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Q8">
-        <v>0.06459001374255612</v>
+        <v>0.08680693396850601</v>
       </c>
       <c r="R8">
-        <v>0.5300751879699248</v>
+        <v>0.6393762183235867</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1365,55 +1380,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>127.4</v>
+        <v>1580.2</v>
       </c>
       <c r="V8">
-        <v>0.5836005497022446</v>
+        <v>2.091041418552336</v>
       </c>
       <c r="W8">
-        <v>0.1045186640471513</v>
+        <v>0.1202813599062134</v>
       </c>
       <c r="X8">
-        <v>0.1726148439813172</v>
+        <v>0.1237306722128205</v>
       </c>
       <c r="Y8">
-        <v>-0.06809617993416596</v>
+        <v>-0.003449312306607097</v>
       </c>
       <c r="Z8">
-        <v>0.242092817026308</v>
+        <v>0.3489005446842849</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.118078107116582</v>
+        <v>0.1013336955610101</v>
       </c>
       <c r="AC8">
-        <v>-0.118078107116582</v>
+        <v>-0.1013336955610101</v>
       </c>
       <c r="AD8">
-        <v>329.1</v>
+        <v>877.8</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>329.1</v>
+        <v>877.8</v>
       </c>
       <c r="AG8">
-        <v>201.7</v>
+        <v>-702.4000000000001</v>
       </c>
       <c r="AH8">
-        <v>0.6012056996711728</v>
+        <v>0.5373737373737374</v>
       </c>
       <c r="AI8">
-        <v>0.5510716677829872</v>
+        <v>0.4704936484965428</v>
       </c>
       <c r="AJ8">
-        <v>0.4802380952380953</v>
+        <v>-13.17823639774861</v>
       </c>
       <c r="AK8">
-        <v>0.4293316304810557</v>
+        <v>-2.460245183887917</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1430,7 +1445,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cairo Amman Bank (ASE:CABK)</t>
+          <t>Arab Banking Corporation (Jordan) (ASE:ABCO)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1439,10 +1454,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0317</v>
+        <v>0.0008899999999999999</v>
       </c>
       <c r="E9">
-        <v>0.0319</v>
+        <v>-0.0625</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1457,28 +1472,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>47.2</v>
+        <v>11.1</v>
       </c>
       <c r="L9">
-        <v>0.2352941176470588</v>
+        <v>0.1910499139414802</v>
       </c>
       <c r="M9">
-        <v>24.1</v>
+        <v>6.18</v>
       </c>
       <c r="N9">
-        <v>0.06720580033463469</v>
+        <v>0.05459363957597173</v>
       </c>
       <c r="O9">
-        <v>0.510593220338983</v>
+        <v>0.5567567567567567</v>
       </c>
       <c r="P9">
-        <v>24.1</v>
+        <v>6.18</v>
       </c>
       <c r="Q9">
-        <v>0.06720580033463469</v>
+        <v>0.05459363957597173</v>
       </c>
       <c r="R9">
-        <v>0.510593220338983</v>
+        <v>0.5567567567567567</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1487,55 +1502,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>502.3</v>
+        <v>349.6</v>
       </c>
       <c r="V9">
-        <v>1.400725041829336</v>
+        <v>3.088339222614841</v>
       </c>
       <c r="W9">
-        <v>0.08892238131122834</v>
+        <v>0.04876977152899824</v>
       </c>
       <c r="X9">
-        <v>0.1743049590539204</v>
+        <v>0.1286182680319293</v>
       </c>
       <c r="Y9">
-        <v>-0.08538257774269206</v>
+        <v>-0.07984849650293102</v>
       </c>
       <c r="Z9">
-        <v>0.3831900668576886</v>
+        <v>0.2540445999125492</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.1182473062674951</v>
+        <v>0.1022951431319218</v>
       </c>
       <c r="AC9">
-        <v>-0.1182473062674951</v>
+        <v>-0.1022951431319218</v>
       </c>
       <c r="AD9">
-        <v>553.1</v>
+        <v>147.2</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>553.1</v>
+        <v>147.2</v>
       </c>
       <c r="AG9">
-        <v>50.80000000000001</v>
+        <v>-202.4</v>
       </c>
       <c r="AH9">
-        <v>0.606668860370736</v>
+        <v>0.565284178187404</v>
       </c>
       <c r="AI9">
-        <v>0.4892525431225122</v>
+        <v>0.3873684210526315</v>
       </c>
       <c r="AJ9">
-        <v>0.1240840254030288</v>
+        <v>2.269058295964125</v>
       </c>
       <c r="AK9">
-        <v>0.08086596625278575</v>
+        <v>-6.657894736842112</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1552,7 +1567,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jordan Kuwait Bank (ASE:JOKB)</t>
+          <t>Invest Bank (ASE:INVB)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1561,10 +1576,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.00153</v>
+        <v>0.0663</v>
       </c>
       <c r="E10">
-        <v>-0.119</v>
+        <v>0.051</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1579,28 +1594,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>20.4</v>
+        <v>33.8</v>
       </c>
       <c r="L10">
-        <v>0.1376518218623482</v>
+        <v>0.3580508474576271</v>
       </c>
       <c r="M10">
-        <v>0.113</v>
+        <v>14.1</v>
       </c>
       <c r="N10">
-        <v>0.0003241537578886976</v>
+        <v>0.06500691562932226</v>
       </c>
       <c r="O10">
-        <v>0.00553921568627451</v>
+        <v>0.4171597633136095</v>
       </c>
       <c r="P10">
-        <v>0.113</v>
+        <v>14.1</v>
       </c>
       <c r="Q10">
-        <v>0.0003241537578886976</v>
+        <v>0.06500691562932226</v>
       </c>
       <c r="R10">
-        <v>0.00553921568627451</v>
+        <v>0.4171597633136095</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1609,182 +1624,60 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>826.7</v>
+        <v>86</v>
       </c>
       <c r="V10">
-        <v>2.371485943775101</v>
+        <v>0.396496081143384</v>
       </c>
       <c r="W10">
-        <v>0.03117359413202934</v>
+        <v>0.1283706798328902</v>
       </c>
       <c r="X10">
-        <v>0.150295565690247</v>
+        <v>0.1469422244092142</v>
       </c>
       <c r="Y10">
-        <v>-0.1191219715582177</v>
+        <v>-0.01857154457632401</v>
       </c>
       <c r="Z10">
-        <v>0.3581440309328178</v>
+        <v>0.203010752688172</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.1200107765873641</v>
+        <v>0.1050574337416683</v>
       </c>
       <c r="AC10">
-        <v>-0.1200107765873641</v>
+        <v>-0.1050574337416683</v>
       </c>
       <c r="AD10">
-        <v>365.2</v>
+        <v>394.9</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>365.2</v>
+        <v>394.9</v>
       </c>
       <c r="AG10">
-        <v>-461.5000000000001</v>
+        <v>308.9</v>
       </c>
       <c r="AH10">
-        <v>0.5116279069767442</v>
+        <v>0.6454723765936581</v>
       </c>
       <c r="AI10">
-        <v>0.3563274465801541</v>
+        <v>0.5768331872626351</v>
       </c>
       <c r="AJ10">
-        <v>4.087688219663418</v>
+        <v>0.5874857360213008</v>
       </c>
       <c r="AK10">
-        <v>-2.328456104944501</v>
+        <v>0.5160374206481791</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Arab Banking Corporation (Jordan) (ASE:ABCO)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>-0.036</v>
-      </c>
-      <c r="E11">
-        <v>-0.135</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>8.48</v>
-      </c>
-      <c r="L11">
-        <v>0.1692614770459082</v>
-      </c>
-      <c r="M11">
-        <v>9.220000000000001</v>
-      </c>
-      <c r="N11">
-        <v>0.07435483870967742</v>
-      </c>
-      <c r="O11">
-        <v>1.087264150943396</v>
-      </c>
-      <c r="P11">
-        <v>9.220000000000001</v>
-      </c>
-      <c r="Q11">
-        <v>0.07435483870967742</v>
-      </c>
-      <c r="R11">
-        <v>1.087264150943396</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>172</v>
-      </c>
-      <c r="V11">
-        <v>1.387096774193548</v>
-      </c>
-      <c r="W11">
-        <v>0.03603909902252444</v>
-      </c>
-      <c r="X11">
-        <v>0.167199732101349</v>
-      </c>
-      <c r="Y11">
-        <v>-0.1311606330788245</v>
-      </c>
-      <c r="Z11">
-        <v>0.1994426751592357</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0.1228630812558658</v>
-      </c>
-      <c r="AC11">
-        <v>-0.1228630812558658</v>
-      </c>
-      <c r="AD11">
-        <v>173.1</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>173.1</v>
-      </c>
-      <c r="AG11">
-        <v>1.099999999999994</v>
-      </c>
-      <c r="AH11">
-        <v>0.5826321104005385</v>
-      </c>
-      <c r="AI11">
-        <v>0.4319940104816571</v>
-      </c>
-      <c r="AJ11">
-        <v>0.008792965627497956</v>
-      </c>
-      <c r="AK11">
-        <v>0.004809794490599014</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
         <v>0</v>
       </c>
     </row>
